--- a/data/airdrops_OP.xlsx
+++ b/data/airdrops_OP.xlsx
@@ -460,155 +460,143 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>174</v>
+        <v>25</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ink</t>
+          <t>Polymarket Activity190</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="D2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | The $125,000 Airdrop Is Almost Here | JOIN NOW</t>
+          <t>Main | Drop Hunting | Polymarket</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://airdrops.io/ink-chain/</t>
+          <t>https://cryptorank.io/drophunting/polymarket-activity190</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>airdrops.io</t>
+          <t>cryptorank.io</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sight</t>
+          <t>Dualmint Activity1286</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="D3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | The $125,000 Airdrop Is Almost Here | JOIN NOW</t>
+          <t>Main | Drop Hunting | DualMint</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://airdrops.io/sight/</t>
+          <t>https://cryptorank.io/drophunting/dualmint-activity1286</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>airdrops.io</t>
+          <t>cryptorank.io</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tread fi</t>
+          <t>Chomp Activity1287</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Review and accept the Genesis Distribution Terms on the registration page | Log in to your account | Kirim your wallet</t>
+          <t>Main | Drop Hunting | Chomp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://airdrops.io/tread-fi/</t>
+          <t>https://cryptorank.io/drophunting/chomp-activity1287</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>airdrops.io</t>
+          <t>cryptorank.io</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rialo</t>
+          <t>Voice Activity1288</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D5" t="b">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | The $125,000 Airdrop Is Almost Here | JOIN NOW</t>
+          <t>Main | Drop Hunting | VOICE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://airdrops.io/rialo/</t>
+          <t>https://cryptorank.io/drophunting/voice-activity1288</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>airdrops.io</t>
+          <t>cryptorank.io</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Forecast Activity1289</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D6" t="b">
         <v>0</v>
@@ -616,17 +604,17 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | The $125,000 Airdrop Is Almost Here | JOIN NOW</t>
+          <t>Main | Drop Hunting | Forecast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://airdrops.io/outcome/</t>
+          <t>https://cryptorank.io/drophunting/forecast-activity1289</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>airdrops.io</t>
+          <t>cryptorank.io</t>
         </is>
       </c>
     </row>

--- a/data/airdrops_OP.xlsx
+++ b/data/airdrops_OP.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,7 +464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Polymarket Activity190</t>
+          <t>Canopy Network Activity1101</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -476,12 +476,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Main | Drop Hunting | Polymarket</t>
+          <t>Main | Drop Hunting | Canopy Network</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://cryptorank.io/drophunting/polymarket-activity190</t>
+          <t>https://cryptorank.io/drophunting/canopy-network-activity1101</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -492,129 +492,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dualmint Activity1286</t>
+          <t>Rexy (prev. T-Rex)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Telegram,Twitter/X,Email</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Main | Drop Hunting | DualMint</t>
+          <t>Create your Rexy account Sign in using Google, Apple, X, Telegram, Facebook, Line, or Discord The referral code is automatically included in the link | Open the active campaign in the Offers Portal Complete the available onboarding activities Earn up to 1,100 PTS from the full offer Finish all activities before September 13, 2026 | Return to the campaign and complete the required daily check-ins Make sure all five check-ins are recorded before the deadline Avoid leaving the campaign until the final days | Add the official Rexy extension to your browser Follow the onboarding instructions Rexy uses the extension to create private, verifiable Proofs on your device | Select the account or activity you want to verify Approve each verification request individually Rexy converts the verified fact into a sealed Proof The underlying account data remains on your device | Complete the badge requirements shown in the Opening Run offer Verify the required accounts or activities Check that each completed badge appears in your Rexy profile</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://cryptorank.io/drophunting/dualmint-activity1286</t>
+          <t>https://airdrops.io/rexy/</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>cryptorank.io</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>25</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Chomp Activity1287</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Main | Drop Hunting | Chomp</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://cryptorank.io/drophunting/chomp-activity1287</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>cryptorank.io</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Voice Activity1288</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D5" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Main | Drop Hunting | VOICE</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://cryptorank.io/drophunting/voice-activity1288</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>cryptorank.io</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Forecast Activity1289</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>20</v>
-      </c>
-      <c r="D6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Main | Drop Hunting | Forecast</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://cryptorank.io/drophunting/forecast-activity1289</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>cryptorank.io</t>
+          <t>airdrops.io</t>
         </is>
       </c>
     </row>

--- a/data/airdrops_OP.xlsx
+++ b/data/airdrops_OP.xlsx
@@ -464,7 +464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Canopy Network Activity1101</t>
+          <t>Jupiter Stattion Activity486</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -476,12 +476,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Main | Drop Hunting | Canopy Network</t>
+          <t>Main | Drop Hunting | Jupiter</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://cryptorank.io/drophunting/canopy-network-activity1101</t>
+          <t>https://cryptorank.io/drophunting/jupiter-stattion-activity486</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -492,32 +492,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rexy (prev. T-Rex)</t>
+          <t>Vangrid</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D3" t="b">
         <v>0</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Telegram,Twitter/X,Email</t>
+          <t>Twitter/X</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Create your Rexy account Sign in using Google, Apple, X, Telegram, Facebook, Line, or Discord The referral code is automatically included in the link | Open the active campaign in the Offers Portal Complete the available onboarding activities Earn up to 1,100 PTS from the full offer Finish all activities before September 13, 2026 | Return to the campaign and complete the required daily check-ins Make sure all five check-ins are recorded before the deadline Avoid leaving the campaign until the final days | Add the official Rexy extension to your browser Follow the onboarding instructions Rexy uses the extension to create private, verifiable Proofs on your device | Select the account or activity you want to verify Approve each verification request individually Rexy converts the verified fact into a sealed Proof The underlying account data remains on your device | Complete the badge requirements shown in the Opening Run offer Verify the required accounts or activities Check that each completed badge appears in your Rexy profile</t>
+          <t>Download the Vangrid App on Android, or open the browser capture tool if you are on iOS. Allow camera and location access, since captures without location data cannot be verified. | Film a location a robot would realistically need to cross. Vangrid accepts: Sidewalks and pedestrian paths Stairs and stairwells Alleys and service lanes Public squares and plazas Skip roads, crowds of people, and private indoor spaces. Recording requirements: Hold the phone vertically at chest level, using both hands Walk at a steady pace and pan smoothly from side to side Record 30 to 60 seconds in daylight | Uploads are gated behind an invite code. Masukkan GRID-01 before uploading. Uploading daily adds a 50-point bonus, with further bonuses at 5, 10, and 50 total videos. | Open the Vangrid Loyalty Hub and connect an EVM wallet. Kamu first login credits PTC on its own. | Work through the quest list: follow Vangrid on X, join the Discord, connect LinkedIn, engage with posts, and publish weekly X posts. Reach Discord through the Hub quest link rather than a forwarded invite. No legitimate verification asks you to sign a wallet transaction, so close any page that does. | Follow Vangrid on X, join the Discord, and submit one in-app video to earn the Grid Operator role and badge, which applies a 1.5x multiplier to your PTC.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://airdrops.io/rexy/</t>
+          <t>https://airdrops.io/vangrid/</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/data/airdrops_OP.xlsx
+++ b/data/airdrops_OP.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,7 +464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jupiter Stattion Activity486</t>
+          <t>Rep Hq Activity1293</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -476,12 +476,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Main | Drop Hunting | Jupiter</t>
+          <t>Main | Drop Hunting | REP</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://cryptorank.io/drophunting/jupiter-stattion-activity486</t>
+          <t>https://cryptorank.io/drophunting/rep-hq-activity1293</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -492,37 +492,97 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vangrid</t>
+          <t>Midas Markets Activity1292</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Twitter/X</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Download the Vangrid App on Android, or open the browser capture tool if you are on iOS. Allow camera and location access, since captures without location data cannot be verified. | Film a location a robot would realistically need to cross. Vangrid accepts: Sidewalks and pedestrian paths Stairs and stairwells Alleys and service lanes Public squares and plazas Skip roads, crowds of people, and private indoor spaces. Recording requirements: Hold the phone vertically at chest level, using both hands Walk at a steady pace and pan smoothly from side to side Record 30 to 60 seconds in daylight | Uploads are gated behind an invite code. Masukkan GRID-01 before uploading. Uploading daily adds a 50-point bonus, with further bonuses at 5, 10, and 50 total videos. | Open the Vangrid Loyalty Hub and connect an EVM wallet. Kamu first login credits PTC on its own. | Work through the quest list: follow Vangrid on X, join the Discord, connect LinkedIn, engage with posts, and publish weekly X posts. Reach Discord through the Hub quest link rather than a forwarded invite. No legitimate verification asks you to sign a wallet transaction, so close any page that does. | Follow Vangrid on X, join the Discord, and submit one in-app video to earn the Grid Operator role and badge, which applies a 1.5x multiplier to your PTC.</t>
+          <t>Main | Drop Hunting | Midas Markets</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://airdrops.io/vangrid/</t>
+          <t>https://cryptorank.io/drophunting/midas-markets-activity1292</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>airdrops.io</t>
+          <t>cryptorank.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Giwa Activity939</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Main | Drop Hunting | GIWA</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://cryptorank.io/drophunting/giwa-activity939</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>cryptorank.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Hertzflow Activity1178</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Main | Drop Hunting | HertzFlow</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://cryptorank.io/drophunting/hertzflow-activity1178</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>cryptorank.io</t>
         </is>
       </c>
     </row>

--- a/data/airdrops_OP.xlsx
+++ b/data/airdrops_OP.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,129 +460,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rep Hq Activity1293</t>
+          <t>Canopy</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Twitter/X</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Main | Drop Hunting | REP</t>
+          <t>Kunjungi submission portal and sign in with the EVM wallet you registered | Create or select a Canopy wallet to receive tokens | The locked portion is already credited to your wallet and releases on its own schedule, so there is nothing further to claim, sign, or pay gas for.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://cryptorank.io/drophunting/rep-hq-activity1293</t>
+          <t>https://airdrops.io/canopy/</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>cryptorank.io</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>25</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Midas Markets Activity1292</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>20</v>
-      </c>
-      <c r="D3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Main | Drop Hunting | Midas Markets</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://cryptorank.io/drophunting/midas-markets-activity1292</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>cryptorank.io</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>25</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Giwa Activity939</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Main | Drop Hunting | GIWA</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://cryptorank.io/drophunting/giwa-activity939</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>cryptorank.io</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Hertzflow Activity1178</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D5" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Main | Drop Hunting | HertzFlow</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://cryptorank.io/drophunting/hertzflow-activity1178</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>cryptorank.io</t>
+          <t>airdrops.io</t>
         </is>
       </c>
     </row>

--- a/data/airdrops_OP.xlsx
+++ b/data/airdrops_OP.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,35 +460,63 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Canopy</t>
+          <t>Arc</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="D2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Twitter/X</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kunjungi submission portal and sign in with the EVM wallet you registered | Create or select a Canopy wallet to receive tokens | The locked portion is already credited to your wallet and releases on its own schedule, so there is nothing further to claim, sign, or pay gas for.</t>
+          <t>Kunjungi Arc House community portal and click “Gabung Community” | Register using your email or LinkedIn account | Create your profile and submit your application for approval | Once approved, start completing tasks to collect points and unlock badges | Review the full contribution rules to understand how badges and points are earned across different activities. | Use MetaMask, Rabby, or any EVM wallet. Add the network via Chainlist or manually from docs.arc.network. Alternative RPC endpoints if needed. Network name: Arc Testnet RPC URL: https://rpc.testnet.arc.network Chain ID: 5042002 Currency symbol: USDC Block Explorer: https://testnet.arcscan.app</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://airdrops.io/canopy/</t>
+          <t>https://airdrops.io/arc/</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>airdrops.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Beezie</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Step 1: Kunjungi Beezie platform | Step 2: Create an account and complete the registration process | Step 3: Connect your wallet or link a payment method for transactions | Step 4: Navigate to the Claw Machines section | Step 5: Select a claw machine and review the displayed odds and available items | Step 6: Purchase pulls and operate the claw machine to win collectibles</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://airdrops.io/beezie/</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>airdrops.io</t>
         </is>
